--- a/backend/storage/notifications.xlsx
+++ b/backend/storage/notifications.xlsx
@@ -456,12 +456,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>58fa6301-5699-4280-b345-146baa7a6c8c</t>
+          <t>95504d0c-7c77-4869-9038-3afa9dafd603</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ranjithagowda9801@gmail.com</t>
+          <t>sahanashaiva01@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Successfully analyzed: Revised_AI_MultiSummarizer_Plan (1).pdf</t>
+          <t>Successfully analyzed: https://www.nasa.gov/humans-in-space/artemis</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -484,19 +484,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-08T22:23:37.747537</t>
+          <t>2026-05-12T21:02:07.351236</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>de9ca898-b1c3-43e8-8fdb-8d67c1d88947</t>
+          <t>bf1658c2-a3e4-4566-b354-419e9b238748</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ranjithagowda9801@gmail.com</t>
+          <t>sahanasahana40163@gmail.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Successfully analyzed: Revised_AI_MultiSummarizer_Plan (1).pdf</t>
+          <t>Successfully analyzed: https://www.nasa.gov/humans-in-space/artemis</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -519,19 +519,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-08T22:41:53.015926</t>
+          <t>2026-05-13T04:49:16.307134</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>c36780f7-e45c-4333-a614-c4ba2f89c7e8</t>
+          <t>14164fd9-51fe-423d-91e5-4145d3024e9c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ranjithagowda9801@gmail.com</t>
+          <t>sahanashaiva01@gmail.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Successfully analyzed: Revised_AI_MultiSummarizer_Plan (1).pdf</t>
+          <t>Successfully analyzed: https://www.nasa.gov/humans-in-space/artemis/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-08T22:43:30.566757</t>
+          <t>2026-05-18T10:23:35.916869</t>
         </is>
       </c>
     </row>
